--- a/output/yearly_surface_area_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_25_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643780135</v>
+        <v>10.84497665080638</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907230982252</v>
+        <v>37.78907305203368</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.846708489417256</v>
+        <v>5.582217446347364</v>
       </c>
       <c r="C2" t="n">
-        <v>9.710466542705202</v>
+        <v>5.132576997802325</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31494539108075</v>
+        <v>25.19851832490288</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.77163800000477</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="C3" t="n">
-        <v>22.26112919379642</v>
+        <v>22.02550974477719</v>
       </c>
       <c r="D3" t="n">
-        <v>73.39054963097031</v>
+        <v>62.70913460876501</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.7078087036955</v>
+        <v>38.10948238345269</v>
       </c>
       <c r="C4" t="n">
-        <v>55.09666291003525</v>
+        <v>69.39090948386881</v>
       </c>
       <c r="D4" t="n">
-        <v>104.1565591866568</v>
+        <v>68.81658707688442</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.21701696703012</v>
+        <v>47.93383165985053</v>
       </c>
       <c r="C5" t="n">
-        <v>95.74494485667019</v>
+        <v>118.349685746953</v>
       </c>
       <c r="D5" t="n">
-        <v>84.47938995043805</v>
+        <v>50.82998738737862</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>45.68562941712533</v>
       </c>
       <c r="C6" t="n">
-        <v>108.0756960220101</v>
+        <v>128.644292173685</v>
       </c>
       <c r="D6" t="n">
-        <v>56.15105994439633</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>31.79978988825843</v>
       </c>
       <c r="C7" t="n">
-        <v>82.82318157337367</v>
+        <v>107.3168050466273</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.7745421853885</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>45.47946239923349</v>
+        <v>68.92850631516855</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.68686521180821</v>
+        <v>7.699686965153233</v>
       </c>
       <c r="C21" t="n">
-        <v>94.16409884465057</v>
+        <v>95.28362619377127</v>
       </c>
       <c r="D21" t="n">
-        <v>7.68686521180821</v>
+        <v>8.662147835797388</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.255516445011429</v>
+        <v>6.649377200863646</v>
       </c>
       <c r="C2" t="n">
-        <v>16.15171323026852</v>
+        <v>7.614435194138261</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04532462531137</v>
+        <v>19.91573392835079</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.75200304591983</v>
+        <v>18.75138115111408</v>
       </c>
       <c r="C3" t="n">
-        <v>30.10529335072844</v>
+        <v>20.83268628411732</v>
       </c>
       <c r="D3" t="n">
-        <v>75.01043334297755</v>
+        <v>67.09754684674826</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.64850293081319</v>
+        <v>36.80768492762142</v>
       </c>
       <c r="C4" t="n">
-        <v>54.75206946584462</v>
+        <v>61.4524975473291</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1242436278747</v>
+        <v>81.43891731038566</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.57383335202821</v>
+        <v>52.59713325502288</v>
       </c>
       <c r="C5" t="n">
-        <v>98.54292581377362</v>
+        <v>122.963899956913</v>
       </c>
       <c r="D5" t="n">
-        <v>100.8009455335413</v>
+        <v>62.58641614573418</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.89446394068941</v>
+        <v>54.50074205355744</v>
       </c>
       <c r="C6" t="n">
-        <v>128.0405173355733</v>
+        <v>155.6531532652191</v>
       </c>
       <c r="D6" t="n">
-        <v>67.50202690089796</v>
+        <v>46.16864928761476</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.91495746929157</v>
+        <v>42.33983324105218</v>
       </c>
       <c r="C7" t="n">
-        <v>117.9167350093801</v>
+        <v>145.1651425407504</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.62008900065226</v>
+        <v>24.78422079371073</v>
       </c>
       <c r="C8" t="n">
-        <v>75.10369937488099</v>
+        <v>102.9755166984479</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3781214015178</v>
+        <v>62.56874468705769</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1237,7 +1237,7 @@
         <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.869173802596139</v>
+        <v>7.882429900379334</v>
       </c>
       <c r="C21" t="n">
-        <v>103.2829061590743</v>
+        <v>104.4421961800262</v>
       </c>
       <c r="D21" t="n">
-        <v>8.852820527920656</v>
+        <v>9.853037375474168</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.770933989741005</v>
+        <v>7.535895377798517</v>
       </c>
       <c r="C2" t="n">
-        <v>15.33293564492668</v>
+        <v>5.98964274360979</v>
       </c>
       <c r="D2" t="n">
-        <v>28.41374205631119</v>
+        <v>23.67779113102457</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.5633275602552</v>
+        <v>20.11601046001715</v>
       </c>
       <c r="C3" t="n">
-        <v>45.322382766554</v>
+        <v>24.8087644863169</v>
       </c>
       <c r="D3" t="n">
-        <v>73.31691855315181</v>
+        <v>66.85210992068656</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.57643443777567</v>
+        <v>35.95258267722244</v>
       </c>
       <c r="C4" t="n">
-        <v>63.46900733185205</v>
+        <v>56.36017220540089</v>
       </c>
       <c r="D4" t="n">
-        <v>123.0709104566759</v>
+        <v>93.24443345395355</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.26734814185396</v>
+        <v>53.4070751110265</v>
       </c>
       <c r="C5" t="n">
-        <v>99.40195505498957</v>
+        <v>118.3251420543468</v>
       </c>
       <c r="D5" t="n">
-        <v>113.8336463074177</v>
+        <v>73.60653412590462</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.99133816824036</v>
+        <v>61.42402686390595</v>
       </c>
       <c r="C6" t="n">
-        <v>139.4719876038232</v>
+        <v>171.7135639589926</v>
       </c>
       <c r="D6" t="n">
-        <v>80.66431837173494</v>
+        <v>53.65545728020094</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.17364014159399</v>
+        <v>52.04146405441917</v>
       </c>
       <c r="C7" t="n">
-        <v>146.5425345698086</v>
+        <v>179.2406236074529</v>
       </c>
       <c r="D7" t="n">
-        <v>54.31715523286327</v>
+        <v>44.19631814978291</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.38356991938679</v>
+        <v>34.04701038327938</v>
       </c>
       <c r="C8" t="n">
-        <v>110.9031294102409</v>
+        <v>142.7804773671348</v>
       </c>
       <c r="D8" t="n">
-        <v>42.39186586937727</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.52656092684155</v>
+        <v>17.08437354930299</v>
       </c>
       <c r="C9" t="n">
-        <v>63.89999457401638</v>
+        <v>90.30311733203008</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>54.37900533823083</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.03615472817418</v>
+        <v>8.05033205709176</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5016468534168</v>
+        <v>112.7046487992846</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04519341021773</v>
+        <v>11.06920657850117</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.074874867430015</v>
+        <v>6.895795874629596</v>
       </c>
       <c r="C2" t="n">
-        <v>10.42616061910113</v>
+        <v>4.024183839707676</v>
       </c>
       <c r="D2" t="n">
-        <v>23.29392777866407</v>
+        <v>19.45529425505904</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.64387192973244</v>
+        <v>24.63204989955247</v>
       </c>
       <c r="C3" t="n">
-        <v>62.54714623756429</v>
+        <v>36.38847865790802</v>
       </c>
       <c r="D3" t="n">
-        <v>81.65195656220722</v>
+        <v>72.28117472517141</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.9158160438088</v>
+        <v>25.65306751196916</v>
       </c>
       <c r="C4" t="n">
-        <v>84.94866535306802</v>
+        <v>90.43663501980767</v>
       </c>
       <c r="D4" t="n">
-        <v>122.4327744489155</v>
+        <v>87.84580282830034</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.85266539556753</v>
+        <v>34.60660657470007</v>
       </c>
       <c r="C5" t="n">
-        <v>83.32583639794804</v>
+        <v>102.5926350937917</v>
       </c>
       <c r="D5" t="n">
-        <v>78.78525326580655</v>
+        <v>52.54804586981054</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.85793398698726</v>
+        <v>32.28182801104362</v>
       </c>
       <c r="C6" t="n">
-        <v>96.52347078613792</v>
+        <v>118.0581066787917</v>
       </c>
       <c r="D6" t="n">
-        <v>35.74347041621788</v>
+        <v>29.10194719698821</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.07441720354028</v>
+        <v>22.51736534460484</v>
       </c>
       <c r="C7" t="n">
-        <v>77.97236616669016</v>
+        <v>100.3699582913769</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>47.06498494159209</v>
+        <v>66.50849822420017</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.030475236560656</v>
+        <v>4.271584261177872</v>
       </c>
       <c r="C2" t="n">
-        <v>4.262748531839651</v>
+        <v>3.203442758957342</v>
       </c>
       <c r="D2" t="n">
-        <v>16.41776685811941</v>
+        <v>13.68654474490478</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.65859814529614</v>
+        <v>24.94620916491145</v>
       </c>
       <c r="C3" t="n">
-        <v>52.30751768227006</v>
+        <v>26.18321127226244</v>
       </c>
       <c r="D3" t="n">
-        <v>81.68140899333463</v>
+        <v>71.5154115158589</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.09145107187775</v>
+        <v>35.26339578884118</v>
       </c>
       <c r="C4" t="n">
-        <v>122.9815714155894</v>
+        <v>93.11680625240146</v>
       </c>
       <c r="D4" t="n">
-        <v>134.8636638800886</v>
+        <v>102.2293884432204</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.12326790904115</v>
+        <v>38.41087892865646</v>
       </c>
       <c r="C5" t="n">
-        <v>118.6196663656209</v>
+        <v>135.505726878666</v>
       </c>
       <c r="D5" t="n">
-        <v>97.43845964649596</v>
+        <v>66.46431957750907</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.0629803884546</v>
+        <v>38.68184129502858</v>
       </c>
       <c r="C6" t="n">
-        <v>115.3209940793516</v>
+        <v>143.0543849766197</v>
       </c>
       <c r="D6" t="n">
-        <v>45.32336451425826</v>
+        <v>35.05919226635785</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="C7" t="n">
-        <v>102.8253092996982</v>
+        <v>128.8160980219282</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>63.92159302350981</v>
+        <v>89.37340225610838</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>47.48124596819272</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.553746762924207</v>
+        <v>4.993168823799278</v>
       </c>
       <c r="C2" t="n">
-        <v>10.70694046251571</v>
+        <v>4.408047192068178</v>
       </c>
       <c r="D2" t="n">
-        <v>24.56038231714246</v>
+        <v>17.59979109403257</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.30669049881928</v>
+        <v>19.63004534641497</v>
       </c>
       <c r="C3" t="n">
-        <v>33.46777923777377</v>
+        <v>18.85446466005999</v>
       </c>
       <c r="D3" t="n">
-        <v>76.90029767365266</v>
+        <v>66.15016031215008</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.46830332158828</v>
+        <v>41.78514578815274</v>
       </c>
       <c r="C4" t="n">
-        <v>126.7848620218416</v>
+        <v>78.66940703670541</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4019236639231</v>
+        <v>113.5754466612007</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.37624002156735</v>
+        <v>45.45491870662732</v>
       </c>
       <c r="C5" t="n">
-        <v>171.5849550097363</v>
+        <v>153.5944283294135</v>
       </c>
       <c r="D5" t="n">
-        <v>119.3314334511998</v>
+        <v>85.65748719553422</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.54978838104078</v>
+        <v>45.44411948188061</v>
       </c>
       <c r="C6" t="n">
-        <v>151.0242128396953</v>
+        <v>179.4821335426977</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18251692866124</v>
+        <v>45.92713935237005</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.83593462686632</v>
+        <v>31.14103717870882</v>
       </c>
       <c r="C7" t="n">
-        <v>133.4273669887755</v>
+        <v>167.0237551758056</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.77177686872501</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>96.38308086443061</v>
+        <v>127.2590461629928</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>54.58124536530566</v>
+        <v>75.10468112258522</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.313398501832985</v>
+        <v>2.933462140289469</v>
       </c>
       <c r="C2" t="n">
-        <v>4.998077562320511</v>
+        <v>2.052834449580081</v>
       </c>
       <c r="D2" t="n">
-        <v>17.11677122354314</v>
+        <v>12.13832861530756</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.7141157960817</v>
+        <v>20.20436775339936</v>
       </c>
       <c r="C3" t="n">
-        <v>39.19136835353267</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="D3" t="n">
-        <v>79.94862429533902</v>
+        <v>67.00918955336604</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.88420449529043</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="C4" t="n">
-        <v>123.3261648597801</v>
+        <v>75.08308267309181</v>
       </c>
       <c r="D4" t="n">
-        <v>151.4041492012389</v>
+        <v>121.182027873705</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.33973543006097</v>
+        <v>48.08109381548755</v>
       </c>
       <c r="C5" t="n">
-        <v>213.3828635180443</v>
+        <v>174.8001787411446</v>
       </c>
       <c r="D5" t="n">
-        <v>125.3691818323177</v>
+        <v>93.3396629812655</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.13719230334986</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>181.615471304026</v>
+        <v>219.8545443844393</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>45.80638438474769</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>134.3256661381613</v>
+        <v>173.7909421011789</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>69.5126461991954</v>
+        <v>95.2148010963769</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62343515439249</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.684900044665779</v>
+        <v>3.887720908817369</v>
       </c>
       <c r="C2" t="n">
-        <v>6.571819132228149</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="D2" t="n">
-        <v>13.87798554723291</v>
+        <v>15.50965023169111</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.75490723130357</v>
+        <v>15.07964473723101</v>
       </c>
       <c r="C3" t="n">
-        <v>29.18245050873644</v>
+        <v>13.28304643845934</v>
       </c>
       <c r="D3" t="n">
-        <v>76.10508203321274</v>
+        <v>61.64393834965722</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.32340557198725</v>
+        <v>43.17628228507048</v>
       </c>
       <c r="C4" t="n">
-        <v>111.8524794402476</v>
+        <v>61.87366731245098</v>
       </c>
       <c r="D4" t="n">
-        <v>155.4626942105952</v>
+        <v>126.1467260140812</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.5316592584746</v>
+        <v>57.80039608753097</v>
       </c>
       <c r="C5" t="n">
-        <v>221.4822820780805</v>
+        <v>158.8222348545278</v>
       </c>
       <c r="D5" t="n">
-        <v>145.4213786915588</v>
+        <v>111.9437819767426</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.25294072145974</v>
+        <v>49.42903341341842</v>
       </c>
       <c r="C6" t="n">
-        <v>251.2105843103782</v>
+        <v>248.795484957931</v>
       </c>
       <c r="D6" t="n">
-        <v>78.28947067516191</v>
+        <v>61.06176196103888</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>21.67895280517807</v>
       </c>
       <c r="C7" t="n">
-        <v>190.139986620001</v>
+        <v>240.2051925457713</v>
       </c>
       <c r="D7" t="n">
-        <v>43.17824578047897</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>112.3217548428776</v>
+        <v>151.7094727372596</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>65.12030697039516</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.386047831947249</v>
+        <v>2.748893571891069</v>
       </c>
       <c r="C2" t="n">
-        <v>3.518583772020568</v>
+        <v>2.205005343738336</v>
       </c>
       <c r="D2" t="n">
-        <v>10.50175519232813</v>
+        <v>12.31995194059322</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10695374650067</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C3" t="n">
-        <v>28.09271055702248</v>
+        <v>11.60916660271853</v>
       </c>
       <c r="D3" t="n">
-        <v>71.88847564347269</v>
+        <v>60.19586048589318</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.84819862540279</v>
+        <v>38.64551662997145</v>
       </c>
       <c r="C4" t="n">
-        <v>97.50718198579321</v>
+        <v>50.82115165804039</v>
       </c>
       <c r="D4" t="n">
-        <v>157.5174921555837</v>
+        <v>128.0994221978281</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.42214548395546</v>
+        <v>62.90548414961439</v>
       </c>
       <c r="C5" t="n">
-        <v>223.1021657900877</v>
+        <v>146.6976507070797</v>
       </c>
       <c r="D5" t="n">
-        <v>158.6013416210722</v>
+        <v>125.7373372214103</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.39006660488482</v>
+        <v>57.9623844587317</v>
       </c>
       <c r="C6" t="n">
-        <v>295.1653925249163</v>
+        <v>262.9238161697468</v>
       </c>
       <c r="D6" t="n">
-        <v>93.46434493970486</v>
+        <v>72.09071567054754</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>246.2537401516359</v>
+        <v>289.6715323719511</v>
       </c>
       <c r="D7" t="n">
-        <v>48.26860762699867</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>146.368765226157</v>
+        <v>196.9385894719101</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>78.65468082114168</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.347178834404876</v>
+        <v>4.788965301315941</v>
       </c>
       <c r="C2" t="n">
-        <v>13.71599717603219</v>
+        <v>6.732825755724625</v>
       </c>
       <c r="D2" t="n">
-        <v>9.759553927917542</v>
+        <v>13.11124059021615</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.34824269756713</v>
+        <v>11.95277829920492</v>
       </c>
       <c r="C3" t="n">
-        <v>21.56408832378119</v>
+        <v>10.07273144557228</v>
       </c>
       <c r="D3" t="n">
-        <v>64.95733685149021</v>
+        <v>56.42594930158543</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.86248287260999</v>
+        <v>33.27241144462865</v>
       </c>
       <c r="C4" t="n">
-        <v>85.3698351181899</v>
+        <v>40.64926369433918</v>
       </c>
       <c r="D4" t="n">
-        <v>156.9559324687546</v>
+        <v>128.5588801234156</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.44039777970866</v>
+        <v>61.08925089675779</v>
       </c>
       <c r="C5" t="n">
-        <v>204.4489594093983</v>
+        <v>122.9393562643069</v>
       </c>
       <c r="D5" t="n">
-        <v>173.1557513365312</v>
+        <v>139.2609118474101</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.54606667886881</v>
+        <v>68.91083485649213</v>
       </c>
       <c r="C6" t="n">
-        <v>319.1956310817655</v>
+        <v>251.5728492132452</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0266496945268</v>
+        <v>89.1574177611741</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.42913122440964</v>
+        <v>38.0279973240002</v>
       </c>
       <c r="C7" t="n">
-        <v>316.0815273638946</v>
+        <v>332.1311388329214</v>
       </c>
       <c r="D7" t="n">
-        <v>58.4493313200381</v>
+        <v>50.12509253572939</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>215.2138229864645</v>
+        <v>271.7919431822082</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>99.51092905016091</v>
+        <v>142.1109254328385</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>54.8060655895782</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.054839002717578</v>
+        <v>5.452626749386785</v>
       </c>
       <c r="C2" t="n">
-        <v>2.512292375167588</v>
+        <v>7.236462328003239</v>
       </c>
       <c r="D2" t="n">
-        <v>21.94107944221196</v>
+        <v>7.420049148697394</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.146501392111027</v>
+        <v>3.388011327355743</v>
       </c>
       <c r="C2" t="n">
-        <v>8.010079518949725</v>
+        <v>3.769911184307752</v>
       </c>
       <c r="D2" t="n">
-        <v>7.261987768313657</v>
+        <v>9.649598185041899</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.9280957378785</v>
+        <v>16.4050041379642</v>
       </c>
       <c r="C3" t="n">
-        <v>33.64940256305943</v>
+        <v>16.48845269282518</v>
       </c>
       <c r="D3" t="n">
-        <v>69.14449081010285</v>
+        <v>61.21196935978863</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.36093296892689</v>
+        <v>46.31591144325178</v>
       </c>
       <c r="C4" t="n">
-        <v>121.48833315743</v>
+        <v>61.3121076256218</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7291898068026</v>
+        <v>132.6940014537031</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.29507375728434</v>
+        <v>41.06159773012285</v>
       </c>
       <c r="C5" t="n">
-        <v>284.0196108386023</v>
+        <v>198.6811916469483</v>
       </c>
       <c r="D5" t="n">
-        <v>159.1167591658018</v>
+        <v>128.2407938672396</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.2252054393668</v>
+        <v>23.58747034223387</v>
       </c>
       <c r="C6" t="n">
-        <v>267.6332599070188</v>
+        <v>272.9867301382766</v>
       </c>
       <c r="D6" t="n">
-        <v>87.74860980557993</v>
+        <v>72.05046401467342</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>151.3334633665331</v>
+        <v>191.0981723793459</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>73.35127972280043</v>
+        <v>104.7279363505285</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
         <v>19.07535789351553</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.464227795388499</v>
+        <v>7.440665850486575</v>
       </c>
       <c r="C2" t="n">
-        <v>4.218569885148544</v>
+        <v>4.474806035956962</v>
       </c>
       <c r="D2" t="n">
-        <v>26.67506687209008</v>
+        <v>10.96906709954961</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.98146996680633</v>
+        <v>11.58462291011236</v>
       </c>
       <c r="C3" t="n">
-        <v>6.327363953870693</v>
+        <v>18.23105486786327</v>
       </c>
       <c r="D3" t="n">
-        <v>21.56408832378119</v>
+        <v>9.370781837035805</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39659538841669</v>
+        <v>13.39855003770922</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13511703347559</v>
+        <v>70.14535019741885</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576070045696081</v>
+        <v>1.576300004436378</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.163011176633976</v>
+        <v>5.771694753266998</v>
       </c>
       <c r="C2" t="n">
-        <v>7.294385442553801</v>
+        <v>5.263149442467151</v>
       </c>
       <c r="D2" t="n">
-        <v>23.56390839733194</v>
+        <v>10.16599747747572</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.48063976892021</v>
+        <v>20.01292695107123</v>
       </c>
       <c r="C3" t="n">
-        <v>12.65963664626262</v>
+        <v>17.92180434102552</v>
       </c>
       <c r="D3" t="n">
-        <v>38.75939936366407</v>
+        <v>16.31664684458199</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.35729941108361</v>
+        <v>13.51572064436584</v>
       </c>
       <c r="C4" t="n">
-        <v>10.21017612416683</v>
+        <v>28.30771330425253</v>
       </c>
       <c r="D4" t="n">
-        <v>26.36777984066083</v>
+        <v>19.98641976305657</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4372773797509</v>
+        <v>15.44302346167581</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12375801334714</v>
+        <v>86.15581510198083</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249953132579138</v>
+        <v>3.251162834037013</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.416302084329653</v>
+        <v>5.605779391249286</v>
       </c>
       <c r="C2" t="n">
-        <v>7.237444075707486</v>
+        <v>9.418887474543899</v>
       </c>
       <c r="D2" t="n">
-        <v>25.0689276279423</v>
+        <v>16.89096925156637</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44842202112931</v>
+        <v>20.00801821255</v>
       </c>
       <c r="C3" t="n">
-        <v>22.19731559302038</v>
+        <v>19.47296571373548</v>
       </c>
       <c r="D3" t="n">
-        <v>48.61614631430206</v>
+        <v>20.66088043587412</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.15379989886403</v>
+        <v>27.70786545695773</v>
       </c>
       <c r="C4" t="n">
-        <v>22.84526907782328</v>
+        <v>38.07119422298706</v>
       </c>
       <c r="D4" t="n">
-        <v>39.84521232456105</v>
+        <v>23.67484588791183</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.87347771933918</v>
+        <v>12.14912784005428</v>
       </c>
       <c r="C5" t="n">
-        <v>13.10633185169492</v>
+        <v>32.05406254365837</v>
       </c>
       <c r="D5" t="n">
-        <v>32.10314992887071</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72926708780539</v>
+        <v>16.74007465277522</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0485292356129</v>
+        <v>102.1144553819288</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182316771951347</v>
+        <v>5.022022395832566</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.469136533909733</v>
+        <v>5.058945919983814</v>
       </c>
       <c r="C2" t="n">
-        <v>6.705336820005715</v>
+        <v>7.287513208624073</v>
       </c>
       <c r="D2" t="n">
-        <v>21.40209995258047</v>
+        <v>13.51768413977433</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.96245690752714</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="C3" t="n">
-        <v>25.58434517267188</v>
+        <v>29.31989518733099</v>
       </c>
       <c r="D3" t="n">
-        <v>56.8530095529328</v>
+        <v>28.9026524130261</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.8422260237193</v>
+        <v>33.57871672835365</v>
       </c>
       <c r="C4" t="n">
-        <v>41.10872161992669</v>
+        <v>43.6612656509684</v>
       </c>
       <c r="D4" t="n">
-        <v>54.42023874180919</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>27.14532402242431</v>
       </c>
       <c r="C5" t="n">
-        <v>28.66703296400687</v>
+        <v>53.11255079975246</v>
       </c>
       <c r="D5" t="n">
-        <v>38.50905369908114</v>
+        <v>31.6122760767473</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.08178815908875</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>16.82519215538184</v>
+        <v>32.56358960216246</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05417154462413</v>
+        <v>18.07015535612598</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7819762673098</v>
+        <v>117.8862516090124</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018057181541377</v>
+        <v>6.883868707095613</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.286932371547326</v>
+        <v>7.063674732055801</v>
       </c>
       <c r="C2" t="n">
-        <v>5.670574739729576</v>
+        <v>9.492518552362409</v>
       </c>
       <c r="D2" t="n">
-        <v>22.91399141712056</v>
+        <v>26.98726264204057</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20927649192059</v>
+        <v>16.35100801423063</v>
       </c>
       <c r="C3" t="n">
-        <v>24.28352946454486</v>
+        <v>27.03242303643592</v>
       </c>
       <c r="D3" t="n">
-        <v>56.8971881996239</v>
+        <v>30.80724295926491</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.94661007553895</v>
+        <v>26.38054256081604</v>
       </c>
       <c r="C4" t="n">
-        <v>45.14174118897259</v>
+        <v>50.79562621772997</v>
       </c>
       <c r="D4" t="n">
-        <v>60.87817514034472</v>
+        <v>31.07722357793278</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.64815877344793</v>
+        <v>23.80738182798515</v>
       </c>
       <c r="C5" t="n">
-        <v>39.90804417763285</v>
+        <v>50.70726892434777</v>
       </c>
       <c r="D5" t="n">
-        <v>39.19627709205391</v>
+        <v>28.17615911188346</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.81260936167588</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>21.57488754852791</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="D6" t="n">
-        <v>32.68434456978482</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>14.61233283000952</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056606279463726</v>
+        <v>7.064702436413921</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15568386997244</v>
+        <v>66.23158534138051</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410378924664829</v>
+        <v>5.29852682731044</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.391177554646736</v>
+        <v>5.430046552189108</v>
       </c>
       <c r="C2" t="n">
-        <v>5.262167694762903</v>
+        <v>5.355433726666351</v>
       </c>
       <c r="D2" t="n">
-        <v>27.44868406303657</v>
+        <v>23.46082488838603</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.65797625049039</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="C3" t="n">
-        <v>23.13979338909732</v>
+        <v>33.63958508601696</v>
       </c>
       <c r="D3" t="n">
-        <v>62.39497534340603</v>
+        <v>46.81463927700915</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.5486834601495</v>
+        <v>29.97962964458485</v>
       </c>
       <c r="C4" t="n">
-        <v>54.64996770460294</v>
+        <v>61.70775195043327</v>
       </c>
       <c r="D4" t="n">
-        <v>75.98923580411162</v>
+        <v>40.48334833232148</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.52668410002858</v>
+        <v>33.45305302221007</v>
       </c>
       <c r="C5" t="n">
-        <v>66.97973712223865</v>
+        <v>77.60715602071038</v>
       </c>
       <c r="D5" t="n">
-        <v>53.70159942230054</v>
+        <v>33.67394625566561</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.52584122104457</v>
+        <v>24.39250345971625</v>
       </c>
       <c r="C6" t="n">
-        <v>46.57116584635595</v>
+        <v>64.44290105446488</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>32.76484788153306</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.75584792127881</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>43.5375654402333</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>19.44351328260808</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279468706776253</v>
+        <v>7.289714908534099</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52448783280363</v>
+        <v>76.54200653960804</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45960153008219</v>
+        <v>6.378500544967336</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.456954650831271</v>
+        <v>5.305364593749763</v>
       </c>
       <c r="C2" t="n">
-        <v>5.893431468593603</v>
+        <v>4.890085314853362</v>
       </c>
       <c r="D2" t="n">
-        <v>25.07678160957628</v>
+        <v>26.5327134549743</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.67484588791183</v>
+        <v>20.0227444281137</v>
       </c>
       <c r="C3" t="n">
-        <v>21.52481841561132</v>
+        <v>26.08994524035899</v>
       </c>
       <c r="D3" t="n">
-        <v>69.87589284976673</v>
+        <v>54.71770829619598</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.15075684476006</v>
+        <v>37.11399021134642</v>
       </c>
       <c r="C4" t="n">
-        <v>56.62818932866027</v>
+        <v>74.41942122502097</v>
       </c>
       <c r="D4" t="n">
-        <v>90.23243149732434</v>
+        <v>54.45852690227482</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.88412237983243</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>85.78020565856507</v>
+        <v>98.83745012504767</v>
       </c>
       <c r="D5" t="n">
-        <v>68.40327129339653</v>
+        <v>41.11068511533519</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.8302651248191</v>
+        <v>35.70321876034376</v>
       </c>
       <c r="C6" t="n">
-        <v>80.02029187774903</v>
+        <v>97.44925887124266</v>
       </c>
       <c r="D6" t="n">
-        <v>46.53091419048183</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.1162314441954</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="C7" t="n">
-        <v>48.14883440708056</v>
+        <v>71.2051792413169</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18958478457343</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8704346652352</v>
+        <v>42.97600575340412</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>24.18437294641592</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489913139693712</v>
+        <v>7.50199095275924</v>
       </c>
       <c r="C21" t="n">
-        <v>85.19776196401597</v>
+        <v>86.27289595673125</v>
       </c>
       <c r="D21" t="n">
-        <v>6.553673997231998</v>
+        <v>7.50199095275924</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_25_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497665080638</v>
+        <v>10.84497618537287</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907305203368</v>
+        <v>37.78907143024126</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.582217446347364</v>
+        <v>6.117269945161876</v>
       </c>
       <c r="C2" t="n">
-        <v>5.132576997802325</v>
+        <v>9.290278525287567</v>
       </c>
       <c r="D2" t="n">
-        <v>25.19851832490288</v>
+        <v>25.04634743074463</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.97227438456961</v>
+        <v>19.62022786937251</v>
       </c>
       <c r="C3" t="n">
-        <v>22.02550974477719</v>
+        <v>41.96971435655114</v>
       </c>
       <c r="D3" t="n">
-        <v>62.70913460876501</v>
+        <v>50.35874848934014</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.10948238345269</v>
+        <v>42.20631555327462</v>
       </c>
       <c r="C4" t="n">
-        <v>69.39090948386881</v>
+        <v>83.04702004994195</v>
       </c>
       <c r="D4" t="n">
-        <v>68.81658707688442</v>
+        <v>52.42925439759667</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.93383165985053</v>
+        <v>49.38190952361457</v>
       </c>
       <c r="C5" t="n">
-        <v>118.349685746953</v>
+        <v>116.8034331127643</v>
       </c>
       <c r="D5" t="n">
-        <v>50.82998738737862</v>
+        <v>41.23340357836604</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>46.97368240509714</v>
       </c>
       <c r="C6" t="n">
-        <v>128.644292173685</v>
+        <v>128.9260537648039</v>
       </c>
       <c r="D6" t="n">
-        <v>40.57366912111219</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.79978988825843</v>
+        <v>35.03366682604743</v>
       </c>
       <c r="C7" t="n">
-        <v>107.3168050466273</v>
+        <v>110.5506819844163</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>18.85937339858123</v>
       </c>
       <c r="C8" t="n">
-        <v>68.92850631516855</v>
+        <v>72.60024272905163</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.15780900513902</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.699686965153233</v>
+        <v>7.704097620917265</v>
       </c>
       <c r="C21" t="n">
-        <v>95.28362619377127</v>
+        <v>95.33820805885117</v>
       </c>
       <c r="D21" t="n">
-        <v>8.662147835797388</v>
+        <v>8.667109823531923</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.649377200863646</v>
+        <v>9.644689446520665</v>
       </c>
       <c r="C2" t="n">
-        <v>7.614435194138261</v>
+        <v>6.718099540160924</v>
       </c>
       <c r="D2" t="n">
-        <v>19.91573392835079</v>
+        <v>22.56154399129595</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75138115111408</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="C3" t="n">
-        <v>20.83268628411732</v>
+        <v>38.72503819401544</v>
       </c>
       <c r="D3" t="n">
-        <v>67.09754684674826</v>
+        <v>57.1573513412493</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.80768492762142</v>
+        <v>39.81968688425063</v>
       </c>
       <c r="C4" t="n">
-        <v>61.4524975473291</v>
+        <v>93.02746721131501</v>
       </c>
       <c r="D4" t="n">
-        <v>81.43891731038566</v>
+        <v>63.13717660781662</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.59713325502288</v>
+        <v>55.49328898255097</v>
       </c>
       <c r="C5" t="n">
-        <v>122.963899956913</v>
+        <v>134.5485228670254</v>
       </c>
       <c r="D5" t="n">
-        <v>62.58641614573418</v>
+        <v>49.70097752749479</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.50074205355744</v>
+        <v>56.07055663264809</v>
       </c>
       <c r="C6" t="n">
-        <v>155.6531532652191</v>
+        <v>154.6468618683661</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>41.57996051796516</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.33983324105218</v>
+        <v>44.91495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>145.1651425407504</v>
+        <v>147.0815140594401</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.78422079371073</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="C8" t="n">
-        <v>102.9755166984479</v>
+        <v>106.8975987769139</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>64.45468202691582</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>39.28954312395736</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.882429900379334</v>
+        <v>7.885712626072488</v>
       </c>
       <c r="C21" t="n">
-        <v>104.4421961800262</v>
+        <v>103.4999782172014</v>
       </c>
       <c r="D21" t="n">
-        <v>9.853037375474168</v>
+        <v>9.857140782590609</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.535895377798517</v>
+        <v>9.74777295546658</v>
       </c>
       <c r="C2" t="n">
-        <v>5.98964274360979</v>
+        <v>14.87740471015616</v>
       </c>
       <c r="D2" t="n">
-        <v>23.67779113102457</v>
+        <v>26.13019689623311</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.11601046001715</v>
+        <v>25.20637230653686</v>
       </c>
       <c r="C3" t="n">
-        <v>24.8087644863169</v>
+        <v>32.43203540979338</v>
       </c>
       <c r="D3" t="n">
-        <v>66.85210992068656</v>
+        <v>61.07943341971531</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.95258267722244</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="C4" t="n">
-        <v>56.36017220540089</v>
+        <v>94.46965458885359</v>
       </c>
       <c r="D4" t="n">
-        <v>93.24443345395355</v>
+        <v>72.91342024670637</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.4070751110265</v>
+        <v>56.94136684631501</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3251420543468</v>
+        <v>149.1765636603029</v>
       </c>
       <c r="D5" t="n">
-        <v>73.60653412590462</v>
+        <v>58.0212893209865</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.42402686390595</v>
+        <v>64.44290105446488</v>
       </c>
       <c r="C6" t="n">
-        <v>171.7135639589926</v>
+        <v>180.4884249395506</v>
       </c>
       <c r="D6" t="n">
-        <v>53.65545728020094</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.04146405441917</v>
+        <v>53.95783557310894</v>
       </c>
       <c r="C7" t="n">
-        <v>179.2406236074529</v>
+        <v>178.8813039476985</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.04701038327938</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="C8" t="n">
-        <v>142.7804773671348</v>
+        <v>144.1991027997715</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>19.52499834206056</v>
       </c>
       <c r="C9" t="n">
-        <v>90.30311733203008</v>
+        <v>94.07499201174633</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>54.37900533823083</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.05033205709176</v>
+        <v>8.050627440279522</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7046487992846</v>
+        <v>111.7024557338784</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06920657850117</v>
+        <v>11.06961273038434</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.895795874629596</v>
+        <v>8.925068379307753</v>
       </c>
       <c r="C2" t="n">
-        <v>4.024183839707676</v>
+        <v>10.11592834455913</v>
       </c>
       <c r="D2" t="n">
-        <v>19.45529425505904</v>
+        <v>21.49045724596268</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.63204989955247</v>
+        <v>28.39705234533899</v>
       </c>
       <c r="C3" t="n">
-        <v>36.38847865790802</v>
+        <v>55.05641125416113</v>
       </c>
       <c r="D3" t="n">
-        <v>72.28117472517141</v>
+        <v>64.31920084372977</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.65306751196916</v>
+        <v>27.35050929261189</v>
       </c>
       <c r="C4" t="n">
-        <v>90.43663501980767</v>
+        <v>126.1594887342364</v>
       </c>
       <c r="D4" t="n">
-        <v>87.84580282830034</v>
+        <v>68.44646819238336</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.60660657470007</v>
+        <v>36.30012136452582</v>
       </c>
       <c r="C5" t="n">
-        <v>102.5926350937917</v>
+        <v>107.8449853115121</v>
       </c>
       <c r="D5" t="n">
-        <v>52.54804586981054</v>
+        <v>43.54051068334605</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28182801104362</v>
+        <v>33.48937768726721</v>
       </c>
       <c r="C6" t="n">
-        <v>118.0581066787917</v>
+        <v>117.816596743547</v>
       </c>
       <c r="D6" t="n">
-        <v>29.10194719698821</v>
+        <v>27.33087433852696</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="C7" t="n">
-        <v>100.3699582913769</v>
+        <v>101.3880306606808</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>66.50849822420017</v>
+        <v>69.34574908947344</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>26.90381408717959</v>
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.271584261177872</v>
+        <v>5.348561492736622</v>
       </c>
       <c r="C2" t="n">
-        <v>3.203442758957342</v>
+        <v>4.618141200776996</v>
       </c>
       <c r="D2" t="n">
-        <v>13.68654474490478</v>
+        <v>14.82242683871834</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.94620916491145</v>
+        <v>30.24764676784423</v>
       </c>
       <c r="C3" t="n">
-        <v>26.18321127226244</v>
+        <v>48.5228802823986</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5154115158589</v>
+        <v>66.47904579307276</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.26339578884118</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="C4" t="n">
-        <v>93.11680625240146</v>
+        <v>134.9912910816407</v>
       </c>
       <c r="D4" t="n">
-        <v>102.2293884432204</v>
+        <v>82.8428165274586</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.41087892865646</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>135.505726878666</v>
+        <v>166.4062358698344</v>
       </c>
       <c r="D5" t="n">
-        <v>66.46431957750907</v>
+        <v>54.04521111878692</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.68184129502858</v>
+        <v>39.72838434775569</v>
       </c>
       <c r="C6" t="n">
-        <v>143.0543849766197</v>
+        <v>144.2216829969692</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05919226635785</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="C7" t="n">
-        <v>128.8160980219282</v>
+        <v>130.5528097107408</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>89.37340225610838</v>
+        <v>91.54306468249383</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>46.92655851529327</v>
       </c>
       <c r="D9" t="n">
         <v>28.84374755077128</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2184,7 +2184,7 @@
         <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.993168823799278</v>
+        <v>5.196390598578367</v>
       </c>
       <c r="C2" t="n">
-        <v>4.408047192068178</v>
+        <v>10.82475018702533</v>
       </c>
       <c r="D2" t="n">
-        <v>17.59979109403257</v>
+        <v>20.3751918539383</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.63004534641497</v>
+        <v>24.19026343264141</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85446466005999</v>
+        <v>32.42712667127215</v>
       </c>
       <c r="D3" t="n">
-        <v>66.15016031215008</v>
+        <v>63.04783756673017</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.78514578815274</v>
+        <v>47.66875977970388</v>
       </c>
       <c r="C4" t="n">
-        <v>78.66940703670541</v>
+        <v>127.8569305148791</v>
       </c>
       <c r="D4" t="n">
-        <v>113.5754466612007</v>
+        <v>95.00568883537234</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.45491870662732</v>
+        <v>48.69468613064181</v>
       </c>
       <c r="C5" t="n">
-        <v>153.5944283294135</v>
+        <v>208.3759502263856</v>
       </c>
       <c r="D5" t="n">
-        <v>85.65748719553422</v>
+        <v>68.55053344903355</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.44411948188061</v>
+        <v>46.97368240509714</v>
       </c>
       <c r="C6" t="n">
-        <v>179.4821335426977</v>
+        <v>199.6482131356314</v>
       </c>
       <c r="D6" t="n">
-        <v>45.92713935237005</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.14103717870882</v>
+        <v>32.5184292077671</v>
       </c>
       <c r="C7" t="n">
-        <v>167.0237551758056</v>
+        <v>167.9819409351505</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C8" t="n">
-        <v>127.2590461629928</v>
+        <v>128.6776715956294</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
         <v>75.10468112258522</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.933462140289469</v>
+        <v>3.140610905885546</v>
       </c>
       <c r="C2" t="n">
-        <v>2.052834449580081</v>
+        <v>5.160065933521236</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13832861530756</v>
+        <v>14.19999879422586</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20436775339936</v>
+        <v>23.74847696573034</v>
       </c>
       <c r="C3" t="n">
-        <v>19.16371518689774</v>
+        <v>38.60722846950582</v>
       </c>
       <c r="D3" t="n">
-        <v>67.00918955336604</v>
+        <v>65.66910393706915</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.26486056263094</v>
+        <v>52.4930679983727</v>
       </c>
       <c r="C4" t="n">
-        <v>75.08308267309181</v>
+        <v>123.6707583039707</v>
       </c>
       <c r="D4" t="n">
-        <v>121.182027873705</v>
+        <v>102.9696262122225</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.08109381548755</v>
+        <v>50.60909415392309</v>
       </c>
       <c r="C5" t="n">
-        <v>174.8001787411446</v>
+        <v>246.7622854624358</v>
       </c>
       <c r="D5" t="n">
-        <v>93.3396629812655</v>
+        <v>73.01748550335654</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.84284791852506</v>
       </c>
       <c r="C6" t="n">
-        <v>219.8545443844393</v>
+        <v>236.8004915074434</v>
       </c>
       <c r="D6" t="n">
-        <v>45.80638438474769</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>173.7909421011789</v>
+        <v>172.7129831219159</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>95.2148010963769</v>
+        <v>94.38031554776711</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2792,7 +2792,7 @@
         <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.887720908817369</v>
+        <v>3.711006322052943</v>
       </c>
       <c r="C2" t="n">
-        <v>2.429825568010856</v>
+        <v>7.618362184955248</v>
       </c>
       <c r="D2" t="n">
-        <v>15.50965023169111</v>
+        <v>17.99249017573129</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07964473723101</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C3" t="n">
-        <v>13.28304643845934</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D3" t="n">
-        <v>61.64393834965722</v>
+        <v>62.61095983834034</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.17628228507048</v>
+        <v>49.58316780298516</v>
       </c>
       <c r="C4" t="n">
-        <v>61.87366731245098</v>
+        <v>110.3592411820882</v>
       </c>
       <c r="D4" t="n">
-        <v>126.1467260140812</v>
+        <v>110.2443767006913</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.80039608753097</v>
+        <v>62.36552291227864</v>
       </c>
       <c r="C5" t="n">
-        <v>158.8222348545278</v>
+        <v>240.0373136883452</v>
       </c>
       <c r="D5" t="n">
-        <v>111.9437819767426</v>
+        <v>88.77453615651784</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.42903341341842</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C6" t="n">
-        <v>248.795484957931</v>
+        <v>306.2748495461732</v>
       </c>
       <c r="D6" t="n">
-        <v>61.06176196103888</v>
+        <v>50.11331156327844</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>21.73883941513712</v>
       </c>
       <c r="C7" t="n">
-        <v>240.2051925457713</v>
+        <v>246.3735133715541</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>151.7094727372596</v>
+        <v>147.7873906587936</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>62.56874468705769</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.34962535589888</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.86995163914969</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.748893571891069</v>
+        <v>2.791108723173682</v>
       </c>
       <c r="C2" t="n">
-        <v>2.205005343738336</v>
+        <v>4.069344234103029</v>
       </c>
       <c r="D2" t="n">
-        <v>12.31995194059322</v>
+        <v>13.20254312671111</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.48568737616169</v>
+        <v>15.55088363526948</v>
       </c>
       <c r="C3" t="n">
-        <v>11.60916660271853</v>
+        <v>29.74204670015712</v>
       </c>
       <c r="D3" t="n">
-        <v>60.19586048589318</v>
+        <v>62.36552291227864</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.64551662997145</v>
+        <v>44.52913062152258</v>
       </c>
       <c r="C4" t="n">
-        <v>50.82115165804039</v>
+        <v>97.86453815013905</v>
       </c>
       <c r="D4" t="n">
-        <v>128.0994221978281</v>
+        <v>114.507125232531</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.90548414961439</v>
+        <v>67.76513528563609</v>
       </c>
       <c r="C5" t="n">
-        <v>146.6976507070797</v>
+        <v>232.3305942100077</v>
       </c>
       <c r="D5" t="n">
-        <v>125.7373372214103</v>
+        <v>100.7764018409351</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.9623844587317</v>
+        <v>59.00892751145879</v>
       </c>
       <c r="C6" t="n">
-        <v>262.9238161697468</v>
+        <v>345.2384524323207</v>
       </c>
       <c r="D6" t="n">
-        <v>72.09071567054754</v>
+        <v>57.80137783523521</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>289.6715323719511</v>
+        <v>312.3685575464331</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>196.9385894719101</v>
+        <v>192.2654703996953</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>78.65468082114168</v>
+        <v>70.77811898996953</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.788965301315941</v>
+        <v>3.926990816987241</v>
       </c>
       <c r="C2" t="n">
-        <v>6.732825755724625</v>
+        <v>16.07906390015426</v>
       </c>
       <c r="D2" t="n">
-        <v>13.11124059021615</v>
+        <v>10.48506548135594</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.95277829920492</v>
+        <v>12.64981916922015</v>
       </c>
       <c r="C3" t="n">
-        <v>10.07273144557228</v>
+        <v>23.27232932917064</v>
       </c>
       <c r="D3" t="n">
-        <v>56.42594930158543</v>
+        <v>59.41046232249573</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.27241144462865</v>
+        <v>37.50963453615788</v>
       </c>
       <c r="C4" t="n">
-        <v>40.64926369433918</v>
+        <v>87.34805674224721</v>
       </c>
       <c r="D4" t="n">
-        <v>128.5588801234156</v>
+        <v>116.3194314945706</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.08925089675779</v>
+        <v>67.17608666308801</v>
       </c>
       <c r="C5" t="n">
-        <v>122.9393562643069</v>
+        <v>210.1185524014236</v>
       </c>
       <c r="D5" t="n">
-        <v>139.2609118474101</v>
+        <v>113.7600152295992</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.91083485649213</v>
+        <v>70.60140440320514</v>
       </c>
       <c r="C6" t="n">
-        <v>251.5728492132452</v>
+        <v>355.7843862713399</v>
       </c>
       <c r="D6" t="n">
-        <v>89.1574177611741</v>
+        <v>70.44039777970866</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.0279973240002</v>
+        <v>35.57264631567892</v>
       </c>
       <c r="C7" t="n">
-        <v>332.1311388329214</v>
+        <v>388.2448923645564</v>
       </c>
       <c r="D7" t="n">
-        <v>50.12509253572939</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>271.7919431822082</v>
+        <v>273.1271200599838</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>142.1109254328385</v>
+        <v>129.3531140161512</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>54.8060655895782</v>
+        <v>48.82722207071512</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.452626749386785</v>
+        <v>7.737153657169113</v>
       </c>
       <c r="C2" t="n">
-        <v>7.236462328003239</v>
+        <v>6.171266068895449</v>
       </c>
       <c r="D2" t="n">
-        <v>7.420049148697394</v>
+        <v>2.525055095322796</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.388011327355743</v>
+        <v>2.873575530330414</v>
       </c>
       <c r="C2" t="n">
-        <v>3.769911184307752</v>
+        <v>9.390416791120741</v>
       </c>
       <c r="D2" t="n">
-        <v>9.649598185041899</v>
+        <v>7.799985510240909</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.4050041379642</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C3" t="n">
-        <v>16.48845269282518</v>
+        <v>38.01817984695773</v>
       </c>
       <c r="D3" t="n">
-        <v>61.21196935978863</v>
+        <v>63.40126674025901</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.31591144325178</v>
+        <v>51.44652494564561</v>
       </c>
       <c r="C4" t="n">
-        <v>61.3121076256218</v>
+        <v>123.9004872667645</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6940014537031</v>
+        <v>116.9192793418654</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.06159773012285</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>198.6811916469483</v>
+        <v>307.4588372774949</v>
       </c>
       <c r="D5" t="n">
-        <v>128.2407938672396</v>
+        <v>103.353489564583</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.58747034223387</v>
+        <v>22.05790741901734</v>
       </c>
       <c r="C6" t="n">
-        <v>272.9867301382766</v>
+        <v>318.4711012760313</v>
       </c>
       <c r="D6" t="n">
-        <v>72.05046401467342</v>
+        <v>59.25043744670351</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.246279805045708</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>191.0981723793459</v>
+        <v>192.0563581386907</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>104.7279363505285</v>
+        <v>95.29824965123788</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.440665850486575</v>
+        <v>7.576147033672636</v>
       </c>
       <c r="C2" t="n">
-        <v>4.474806035956962</v>
+        <v>6.126105674500097</v>
       </c>
       <c r="D2" t="n">
-        <v>10.96906709954961</v>
+        <v>9.519025740377073</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.58462291011236</v>
+        <v>16.42954783057037</v>
       </c>
       <c r="C3" t="n">
-        <v>18.23105486786327</v>
+        <v>15.79632056133118</v>
       </c>
       <c r="D3" t="n">
-        <v>9.370781837035805</v>
+        <v>5.360342465187586</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39855003770922</v>
+        <v>13.39918236158493</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14535019741885</v>
+        <v>70.1486605988858</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576300004436378</v>
+        <v>1.57637439548058</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.771694753266998</v>
+        <v>5.060909415392308</v>
       </c>
       <c r="C2" t="n">
-        <v>5.263149442467151</v>
+        <v>7.099999397112932</v>
       </c>
       <c r="D2" t="n">
-        <v>10.16599747747572</v>
+        <v>8.745408549430588</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.01292695107123</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="C3" t="n">
-        <v>17.92180434102552</v>
+        <v>20.95049600862693</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31664684458199</v>
+        <v>12.06077054667207</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.51572064436584</v>
+        <v>18.97816487079509</v>
       </c>
       <c r="C4" t="n">
-        <v>28.30771330425253</v>
+        <v>25.00216878405352</v>
       </c>
       <c r="D4" t="n">
-        <v>19.98641976305657</v>
+        <v>17.88057093744716</v>
       </c>
     </row>
     <row r="5">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44302346167581</v>
+        <v>15.4439804237546</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15581510198083</v>
+        <v>86.16115394305197</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251162834037013</v>
+        <v>3.25136429973781</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.605779391249286</v>
+        <v>4.767366851822511</v>
       </c>
       <c r="C2" t="n">
-        <v>9.418887474543899</v>
+        <v>5.203262832508095</v>
       </c>
       <c r="D2" t="n">
-        <v>16.89096925156637</v>
+        <v>10.98084807200057</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.00801821255</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C3" t="n">
-        <v>19.47296571373548</v>
+        <v>25.00020528864503</v>
       </c>
       <c r="D3" t="n">
-        <v>20.66088043587412</v>
+        <v>16.25774198232718</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.70786545695773</v>
+        <v>32.62151271671301</v>
       </c>
       <c r="C4" t="n">
-        <v>38.07119422298706</v>
+        <v>41.17253522070273</v>
       </c>
       <c r="D4" t="n">
-        <v>23.67484588791183</v>
+        <v>19.92260616228052</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.14912784005428</v>
+        <v>16.44427404613408</v>
       </c>
       <c r="C5" t="n">
-        <v>32.05406254365837</v>
+        <v>28.56885819358219</v>
       </c>
       <c r="D5" t="n">
-        <v>29.62423697564751</v>
+        <v>28.8879261974624</v>
       </c>
     </row>
     <row r="6">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74007465277522</v>
+        <v>16.7409577619093</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1144553819288</v>
+        <v>102.1198423476467</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022022395832566</v>
+        <v>5.02228732857279</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.058945919983814</v>
+        <v>5.358378969779091</v>
       </c>
       <c r="C2" t="n">
-        <v>7.287513208624073</v>
+        <v>9.535715451349269</v>
       </c>
       <c r="D2" t="n">
-        <v>13.51768413977433</v>
+        <v>14.97361598517235</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.57114048416017</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="C3" t="n">
-        <v>29.31989518733099</v>
+        <v>22.18258937745668</v>
       </c>
       <c r="D3" t="n">
-        <v>28.9026524130261</v>
+        <v>20.98485717827557</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.57871672835365</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="C4" t="n">
-        <v>43.6612656509684</v>
+        <v>53.34817024877168</v>
       </c>
       <c r="D4" t="n">
-        <v>28.20561154301086</v>
+        <v>23.18986252201391</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.14532402242431</v>
+        <v>33.08489763311751</v>
       </c>
       <c r="C5" t="n">
-        <v>53.11255079975246</v>
+        <v>54.68334712654735</v>
       </c>
       <c r="D5" t="n">
-        <v>31.6122760767473</v>
+        <v>29.72241174607219</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.18996033300515</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>32.56358960216246</v>
+        <v>29.54471541160352</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07015535612598</v>
+        <v>18.07230560068284</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8862516090124</v>
+        <v>117.9002793949309</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883868707095613</v>
+        <v>6.884687847879175</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.063674732055801</v>
+        <v>7.935466693426968</v>
       </c>
       <c r="C2" t="n">
-        <v>9.492518552362409</v>
+        <v>8.448920742748049</v>
       </c>
       <c r="D2" t="n">
-        <v>26.98726264204057</v>
+        <v>15.93965572615121</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35100801423063</v>
+        <v>16.20865459711484</v>
       </c>
       <c r="C3" t="n">
-        <v>27.03242303643592</v>
+        <v>29.03027961457818</v>
       </c>
       <c r="D3" t="n">
-        <v>30.80724295926491</v>
+        <v>26.05558407071035</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.38054256081604</v>
+        <v>25.55096575072749</v>
       </c>
       <c r="C4" t="n">
-        <v>50.79562621772997</v>
+        <v>45.74158903626739</v>
       </c>
       <c r="D4" t="n">
-        <v>31.07722357793278</v>
+        <v>24.38955821660351</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.80738182798515</v>
+        <v>26.50718801466389</v>
       </c>
       <c r="C5" t="n">
-        <v>50.70726892434777</v>
+        <v>58.48761948050374</v>
       </c>
       <c r="D5" t="n">
-        <v>28.17615911188346</v>
+        <v>25.54998400302325</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.24279478258523</v>
+        <v>16.26166897314417</v>
       </c>
       <c r="C6" t="n">
-        <v>40.25165587411923</v>
+        <v>40.13090090649688</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>29.98748362621883</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>22.15804568485051</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064702436413921</v>
+        <v>7.065595775749789</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23158534138051</v>
+        <v>66.23996039765427</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29852682731044</v>
+        <v>5.299196831812342</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.430046552189108</v>
+        <v>6.531567476354029</v>
       </c>
       <c r="C2" t="n">
-        <v>5.355433726666351</v>
+        <v>10.16599747747572</v>
       </c>
       <c r="D2" t="n">
-        <v>23.46082488838603</v>
+        <v>19.02921575141593</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.51990967709008</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="C3" t="n">
-        <v>33.63958508601696</v>
+        <v>31.66136346195963</v>
       </c>
       <c r="D3" t="n">
-        <v>46.81463927700915</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.97962964458485</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>61.70775195043327</v>
+        <v>63.06060028688537</v>
       </c>
       <c r="D4" t="n">
-        <v>40.48334833232148</v>
+        <v>32.80019079888594</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>33.99301425954582</v>
       </c>
       <c r="C5" t="n">
-        <v>77.60715602071038</v>
+        <v>74.24467013366505</v>
       </c>
       <c r="D5" t="n">
-        <v>33.67394625566561</v>
+        <v>29.05973204570559</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.39250345971625</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="C6" t="n">
-        <v>64.44290105446488</v>
+        <v>72.29197394991814</v>
       </c>
       <c r="D6" t="n">
-        <v>32.76484788153306</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>14.01346673041897</v>
       </c>
       <c r="C7" t="n">
-        <v>43.5375654402333</v>
+        <v>43.23813239043802</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>25.2849121228766</v>
+        <v>24.28352946454485</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6199,7 +6199,7 @@
         <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6241,7 +6241,7 @@
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289714908534099</v>
+        <v>7.292259561152473</v>
       </c>
       <c r="C21" t="n">
-        <v>76.54200653960804</v>
+        <v>76.56872539210097</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378500544967336</v>
+        <v>6.380727116008414</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.305364593749763</v>
+        <v>4.895975801078843</v>
       </c>
       <c r="C2" t="n">
-        <v>4.890085314853362</v>
+        <v>11.90074567087984</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5327134549743</v>
+        <v>24.33556209286994</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0227444281137</v>
+        <v>23.06616231127881</v>
       </c>
       <c r="C3" t="n">
-        <v>26.08994524035899</v>
+        <v>36.55537576762998</v>
       </c>
       <c r="D3" t="n">
-        <v>54.71770829619598</v>
+        <v>40.97814917526187</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.11399021134642</v>
+        <v>39.21983903695583</v>
       </c>
       <c r="C4" t="n">
-        <v>74.41942122502097</v>
+        <v>72.8368439257751</v>
       </c>
       <c r="D4" t="n">
-        <v>54.45852690227482</v>
+        <v>41.92553570986004</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>40.10439371848221</v>
       </c>
       <c r="C5" t="n">
-        <v>98.83745012504767</v>
+        <v>98.86199381765383</v>
       </c>
       <c r="D5" t="n">
-        <v>41.11068511533519</v>
+        <v>34.70478134512475</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.70321876034376</v>
+        <v>38.27932473628739</v>
       </c>
       <c r="C6" t="n">
-        <v>97.44925887124266</v>
+        <v>98.01278205348032</v>
       </c>
       <c r="D6" t="n">
-        <v>36.38749691020379</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>71.2051792413169</v>
+        <v>76.77463396750906</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97600575340412</v>
+        <v>42.89255719854314</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.50199095275924</v>
+        <v>7.505917542943735</v>
       </c>
       <c r="C21" t="n">
-        <v>86.27289595673125</v>
+        <v>86.31805174385296</v>
       </c>
       <c r="D21" t="n">
-        <v>7.50199095275924</v>
+        <v>7.505917542943735</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_25_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_25_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497618537287</v>
+        <v>10.84497639547321</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907143024126</v>
+        <v>37.78907216233107</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.117269945161876</v>
+        <v>1.183005983617406</v>
       </c>
       <c r="C2" t="n">
-        <v>9.290278525287567</v>
+        <v>4.546473618366979</v>
       </c>
       <c r="D2" t="n">
-        <v>25.04634743074463</v>
+        <v>18.81912174270711</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.62022786937251</v>
+        <v>9.390416791120741</v>
       </c>
       <c r="C3" t="n">
-        <v>41.96971435655114</v>
+        <v>50.60418541540184</v>
       </c>
       <c r="D3" t="n">
-        <v>50.35874848934014</v>
+        <v>66.31705742187204</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.20631555327462</v>
+        <v>16.33628179866692</v>
       </c>
       <c r="C4" t="n">
-        <v>83.04702004994195</v>
+        <v>156.8793561478233</v>
       </c>
       <c r="D4" t="n">
-        <v>52.42925439759667</v>
+        <v>65.89392416134166</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.38190952361457</v>
+        <v>16.10066234964769</v>
       </c>
       <c r="C5" t="n">
-        <v>116.8034331127643</v>
+        <v>216.22993186036</v>
       </c>
       <c r="D5" t="n">
-        <v>41.23340357836604</v>
+        <v>41.20885988575987</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.97368240509714</v>
+        <v>11.02895370950867</v>
       </c>
       <c r="C6" t="n">
-        <v>128.9260537648039</v>
+        <v>154.9286234594849</v>
       </c>
       <c r="D6" t="n">
-        <v>37.47429161880501</v>
+        <v>28.41766904712818</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.03366682604743</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>110.5506819844163</v>
+        <v>70.12722026205391</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>28.80545939030566</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.85937339858123</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>72.60024272905163</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>41.15780900513902</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.31819373382975</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.0832529328785</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>10.70104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.704097620917265</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.33820805885117</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.667109823531923</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.644689446520665</v>
+        <v>1.225221134900019</v>
       </c>
       <c r="C2" t="n">
-        <v>6.718099540160924</v>
+        <v>6.456954650831271</v>
       </c>
       <c r="D2" t="n">
-        <v>22.56154399129595</v>
+        <v>14.83813480198629</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96874830438012</v>
+        <v>6.670975650357076</v>
       </c>
       <c r="C3" t="n">
-        <v>38.72503819401544</v>
+        <v>32.95236169304419</v>
       </c>
       <c r="D3" t="n">
-        <v>57.1573513412493</v>
+        <v>66.39068849969055</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.81968688425063</v>
+        <v>17.21690948937631</v>
       </c>
       <c r="C4" t="n">
-        <v>93.02746721131501</v>
+        <v>140.9770068344335</v>
       </c>
       <c r="D4" t="n">
-        <v>63.13717660781662</v>
+        <v>80.63486594060753</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.49328898255097</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="C5" t="n">
-        <v>134.5485228670254</v>
+        <v>254.8126166372597</v>
       </c>
       <c r="D5" t="n">
-        <v>49.70097752749479</v>
+        <v>53.8979489631499</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.07055663264809</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>154.6468618683661</v>
+        <v>245.0118293057638</v>
       </c>
       <c r="D6" t="n">
-        <v>41.57996051796516</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.91495746929157</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>147.0815140594401</v>
+        <v>139.2363681548039</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.95526587842792</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>106.8975987769139</v>
+        <v>59.41537106101696</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>24.72531593145592</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.885712626072488</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4999782172014</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.857140782590609</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.74777295546658</v>
+        <v>0.6882051406770141</v>
       </c>
       <c r="C2" t="n">
-        <v>14.87740471015616</v>
+        <v>3.002184479586747</v>
       </c>
       <c r="D2" t="n">
-        <v>26.13019689623311</v>
+        <v>10.25730001397068</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.20637230653686</v>
+        <v>6.356816384998098</v>
       </c>
       <c r="C3" t="n">
-        <v>32.43203540979338</v>
+        <v>31.66627220048087</v>
       </c>
       <c r="D3" t="n">
-        <v>61.07943341971531</v>
+        <v>65.66910393706915</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.17329598422873</v>
+        <v>18.64633414675967</v>
       </c>
       <c r="C4" t="n">
-        <v>94.46965458885359</v>
+        <v>132.9875440172729</v>
       </c>
       <c r="D4" t="n">
-        <v>72.91342024670637</v>
+        <v>91.15134734849936</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.94136684631501</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C5" t="n">
-        <v>149.1765636603029</v>
+        <v>297.101398997691</v>
       </c>
       <c r="D5" t="n">
-        <v>58.0212893209865</v>
+        <v>59.39573610693204</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.44290105446488</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>180.4884249395506</v>
+        <v>281.5200811835899</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>34.69692736349078</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.95783557310894</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>178.8813039476985</v>
+        <v>121.5698182168825</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.63391558396972</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>144.1991027997715</v>
+        <v>43.14290286312608</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.52499834206056</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>94.07499201174633</v>
+        <v>24.73906039931537</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.050627440279522</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7024557338784</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06961273038434</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.925068379307753</v>
+        <v>0.828595062384308</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11592834455913</v>
+        <v>6.898741117742336</v>
       </c>
       <c r="D2" t="n">
-        <v>21.49045724596268</v>
+        <v>9.946085991724436</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.39705234533899</v>
+        <v>4.427682146153115</v>
       </c>
       <c r="C3" t="n">
-        <v>55.05641125416113</v>
+        <v>21.50518346152638</v>
       </c>
       <c r="D3" t="n">
-        <v>64.31920084372977</v>
+        <v>59.29756133650734</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.35050929261189</v>
+        <v>15.64709491028566</v>
       </c>
       <c r="C4" t="n">
-        <v>126.1594887342364</v>
+        <v>106.3900352138184</v>
       </c>
       <c r="D4" t="n">
-        <v>68.44646819238336</v>
+        <v>102.2421511633756</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.30012136452582</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="C5" t="n">
-        <v>107.8449853115121</v>
+        <v>275.1102504225625</v>
       </c>
       <c r="D5" t="n">
-        <v>43.54051068334605</v>
+        <v>74.26921382627121</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.48937768726721</v>
+        <v>17.46921864936775</v>
       </c>
       <c r="C6" t="n">
-        <v>117.816596743547</v>
+        <v>371.3215254387499</v>
       </c>
       <c r="D6" t="n">
-        <v>27.33087433852696</v>
+        <v>42.66675522656639</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>101.3880306606808</v>
+        <v>239.1871201764674</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>69.34574908947344</v>
+        <v>90.12443924985719</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.17539834835747</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
+        <v>19.77239876353076</v>
+      </c>
+      <c r="D13" t="n">
         <v>23.15451960466103</v>
-      </c>
-      <c r="D13" t="n">
-        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.348561492736622</v>
+        <v>0.5615596868291756</v>
       </c>
       <c r="C2" t="n">
-        <v>4.618141200776996</v>
+        <v>4.968625131193107</v>
       </c>
       <c r="D2" t="n">
-        <v>14.82242683871834</v>
+        <v>7.258060777496669</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.24764676784423</v>
+        <v>3.799363615435157</v>
       </c>
       <c r="C3" t="n">
-        <v>48.5228802823986</v>
+        <v>24.391521712012</v>
       </c>
       <c r="D3" t="n">
-        <v>66.47904579307276</v>
+        <v>54.91896657556657</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.86248287260999</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="C4" t="n">
-        <v>134.9912910816407</v>
+        <v>86.88859881665971</v>
       </c>
       <c r="D4" t="n">
-        <v>82.8428165274586</v>
+        <v>108.0747142743059</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="C5" t="n">
-        <v>166.4062358698344</v>
+        <v>252.260072606218</v>
       </c>
       <c r="D5" t="n">
-        <v>54.04521111878692</v>
+        <v>85.63294350292804</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="C6" t="n">
-        <v>144.2216829969692</v>
+        <v>415.1555786856658</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>50.2340665309008</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.93657161431823</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>130.5528097107408</v>
+        <v>329.1368083349686</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>135.0197617650638</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>46.92655851529327</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.34073287329842</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>15.97892563432109</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.196390598578367</v>
+        <v>0.5340707511102649</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82475018702533</v>
+        <v>8.453829481269283</v>
       </c>
       <c r="D2" t="n">
-        <v>20.3751918539383</v>
+        <v>10.18661417926491</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.19026343264141</v>
+        <v>2.901064466049325</v>
       </c>
       <c r="C3" t="n">
-        <v>32.42712667127215</v>
+        <v>22.0549621759046</v>
       </c>
       <c r="D3" t="n">
-        <v>63.04783756673017</v>
+        <v>49.16592502868026</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.66875977970388</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="C4" t="n">
-        <v>127.8569305148791</v>
+        <v>75.15965899402306</v>
       </c>
       <c r="D4" t="n">
-        <v>95.00568883537234</v>
+        <v>109.7849187751038</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.69468613064181</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="C5" t="n">
-        <v>208.3759502263856</v>
+        <v>212.6710964324654</v>
       </c>
       <c r="D5" t="n">
-        <v>68.55053344903355</v>
+        <v>99.45104244020192</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.97368240509714</v>
+        <v>25.47929816831747</v>
       </c>
       <c r="C6" t="n">
-        <v>199.6482131356314</v>
+        <v>411.0901614423797</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>60.82025202579416</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.5184292077671</v>
+        <v>12.93550775115597</v>
       </c>
       <c r="C7" t="n">
-        <v>167.9819409351505</v>
+        <v>439.6276037094259</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>41.44153409166636</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>128.6776715956294</v>
+        <v>245.9228911753048</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>75.10468112258522</v>
+        <v>87.30780508637307</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>19.66637001147211</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.28621266575034</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>9.675123625352315</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.140610905885546</v>
+        <v>0.3799363615435156</v>
       </c>
       <c r="C2" t="n">
-        <v>5.160065933521236</v>
+        <v>4.868486865359933</v>
       </c>
       <c r="D2" t="n">
-        <v>14.19999879422586</v>
+        <v>7.496625469628643</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.74847696573034</v>
+        <v>4.030074325933156</v>
       </c>
       <c r="C3" t="n">
-        <v>38.60722846950582</v>
+        <v>28.51977080836984</v>
       </c>
       <c r="D3" t="n">
-        <v>65.66910393706915</v>
+        <v>53.2941741250381</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.4930679983727</v>
+        <v>16.32351907851172</v>
       </c>
       <c r="C4" t="n">
-        <v>123.6707583039707</v>
+        <v>112.6820562503362</v>
       </c>
       <c r="D4" t="n">
-        <v>102.9696262122225</v>
+        <v>110.4230547828642</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.60909415392309</v>
+        <v>14.7753029489145</v>
       </c>
       <c r="C5" t="n">
-        <v>246.7622854624358</v>
+        <v>335.7577148524092</v>
       </c>
       <c r="D5" t="n">
-        <v>73.01748550335654</v>
+        <v>89.75628386076465</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.84284791852506</v>
+        <v>8.010079518949729</v>
       </c>
       <c r="C6" t="n">
-        <v>236.8004915074434</v>
+        <v>366.0888101751144</v>
       </c>
       <c r="D6" t="n">
-        <v>39.92964262712628</v>
+        <v>53.53470231257858</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>172.7129831219159</v>
+        <v>172.9525295617521</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>94.38031554776711</v>
+        <v>64.33883579781471</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>25.4046853427947</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2792,7 +2792,7 @@
         <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.26832022289564</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>7.989462817160544</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.711006322052943</v>
+        <v>0.2100940087088174</v>
       </c>
       <c r="C2" t="n">
-        <v>7.618362184955248</v>
+        <v>3.11803070868787</v>
       </c>
       <c r="D2" t="n">
-        <v>17.99249017573129</v>
+        <v>6.029894399483909</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36711688812607</v>
+        <v>2.719441140763665</v>
       </c>
       <c r="C3" t="n">
-        <v>29.38370878810703</v>
+        <v>23.6699371493906</v>
       </c>
       <c r="D3" t="n">
-        <v>62.61095983834034</v>
+        <v>47.60494617892783</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.58316780298516</v>
+        <v>11.43539725906685</v>
       </c>
       <c r="C4" t="n">
-        <v>110.3592411820882</v>
+        <v>88.6753796383889</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2443767006913</v>
+        <v>106.6708150572329</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.36552291227864</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C5" t="n">
-        <v>240.0373136883452</v>
+        <v>251.7691987540946</v>
       </c>
       <c r="D5" t="n">
-        <v>88.77453615651784</v>
+        <v>93.80599314078275</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.31456984264904</v>
+        <v>7.768569583705012</v>
       </c>
       <c r="C6" t="n">
-        <v>306.2748495461732</v>
+        <v>358.0787306561647</v>
       </c>
       <c r="D6" t="n">
-        <v>50.11331156327844</v>
+        <v>55.34602682691394</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.73883941513712</v>
+        <v>2.575124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>246.3735133715541</v>
+        <v>225.7126329356799</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>30.3625112492411</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>0.9179341034707675</v>
       </c>
       <c r="C8" t="n">
-        <v>147.7873906587936</v>
+        <v>78.69198723390308</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>12.08335074386974</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>7.804894248762142</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.791108723173682</v>
+        <v>0.2051852701875834</v>
       </c>
       <c r="C2" t="n">
-        <v>4.069344234103029</v>
+        <v>13.18094467721768</v>
       </c>
       <c r="D2" t="n">
-        <v>13.20254312671111</v>
+        <v>11.19192382841364</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.55088363526948</v>
+        <v>1.673879835740812</v>
       </c>
       <c r="C3" t="n">
-        <v>29.74204670015712</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="D3" t="n">
-        <v>62.36552291227864</v>
+        <v>41.81263472387165</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.52913062152258</v>
+        <v>8.295768100885548</v>
       </c>
       <c r="C4" t="n">
-        <v>97.86453815013905</v>
+        <v>72.76026760484386</v>
       </c>
       <c r="D4" t="n">
-        <v>114.507125232531</v>
+        <v>106.3772724936631</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.76513528563609</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="C5" t="n">
-        <v>232.3305942100077</v>
+        <v>208.3759502263856</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7764018409351</v>
+        <v>109.121257327033</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.00892751145879</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>345.2384524323207</v>
+        <v>380.1768897310562</v>
       </c>
       <c r="D6" t="n">
-        <v>57.80137783523521</v>
+        <v>69.71586797397451</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>312.3685575464331</v>
+        <v>369.2009503975768</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>192.2654703996953</v>
+        <v>181.0833640483242</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>58.46405753560178</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.926990816987241</v>
+        <v>0.2140209995258046</v>
       </c>
       <c r="C2" t="n">
-        <v>16.07906390015426</v>
+        <v>10.19250466549039</v>
       </c>
       <c r="D2" t="n">
-        <v>10.48506548135594</v>
+        <v>11.87227498745668</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.64981916922015</v>
+        <v>1.183005983617406</v>
       </c>
       <c r="C3" t="n">
-        <v>23.27232932917064</v>
+        <v>34.4102570338507</v>
       </c>
       <c r="D3" t="n">
-        <v>59.41046232249573</v>
+        <v>40.87997440483718</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.50963453615788</v>
+        <v>5.794274950464675</v>
       </c>
       <c r="C4" t="n">
-        <v>87.34805674224721</v>
+        <v>57.59815606045612</v>
       </c>
       <c r="D4" t="n">
-        <v>116.3194314945706</v>
+        <v>102.4718801261693</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.17608666308801</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C5" t="n">
-        <v>210.1185524014236</v>
+        <v>173.1557513365312</v>
       </c>
       <c r="D5" t="n">
-        <v>113.7600152295992</v>
+        <v>120.4604433110837</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.60140440320514</v>
+        <v>16.98619877887832</v>
       </c>
       <c r="C6" t="n">
-        <v>355.7843862713399</v>
+        <v>359.9705584822483</v>
       </c>
       <c r="D6" t="n">
-        <v>70.44039777970866</v>
+        <v>83.80394752991624</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.57264631567892</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>388.2448923645564</v>
+        <v>448.1913889335708</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>46.95110220789945</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>273.1271200599838</v>
+        <v>318.1893396849125</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>129.3531140161512</v>
+        <v>129.7968639784708</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>22.96406055003713</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>19.36890045708532</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.737153657169113</v>
+        <v>5.6018524004323</v>
       </c>
       <c r="C2" t="n">
-        <v>6.171266068895449</v>
+        <v>27.35639977883737</v>
       </c>
       <c r="D2" t="n">
-        <v>2.525055095322796</v>
+        <v>8.552985999398212</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.873575530330414</v>
+        <v>0.4221515128261284</v>
       </c>
       <c r="C2" t="n">
-        <v>9.390416791120741</v>
+        <v>14.15091140901352</v>
       </c>
       <c r="D2" t="n">
-        <v>7.799985510240909</v>
+        <v>11.64843651088841</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98423528346982</v>
+        <v>0.9522952731194061</v>
       </c>
       <c r="C3" t="n">
-        <v>38.01817984695773</v>
+        <v>36.35902622678062</v>
       </c>
       <c r="D3" t="n">
-        <v>63.40126674025901</v>
+        <v>40.47745784609599</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.44652494564561</v>
+        <v>4.198934931063608</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9004872667645</v>
+        <v>68.99526515905734</v>
       </c>
       <c r="D4" t="n">
-        <v>116.9192793418654</v>
+        <v>99.8938106548172</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>12.2963899956913</v>
       </c>
       <c r="C5" t="n">
-        <v>307.4588372774949</v>
+        <v>144.3905436020997</v>
       </c>
       <c r="D5" t="n">
-        <v>103.353489564583</v>
+        <v>125.9336867622596</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.05790741901734</v>
+        <v>17.99249017573129</v>
       </c>
       <c r="C6" t="n">
-        <v>318.4711012760313</v>
+        <v>324.2270880660304</v>
       </c>
       <c r="D6" t="n">
-        <v>59.25043744670351</v>
+        <v>97.97253039760622</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.587527095496098</v>
+        <v>13.71403368062369</v>
       </c>
       <c r="C7" t="n">
-        <v>192.0563581386907</v>
+        <v>481.3685708508875</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>55.87420709179872</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>95.29824965123788</v>
+        <v>426.0048725652972</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>233.0796677083479</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>24.51718541815559</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>82.99204217850412</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.576147033672636</v>
+        <v>4.740859663807847</v>
       </c>
       <c r="C2" t="n">
-        <v>6.126105674500097</v>
+        <v>18.09066494615598</v>
       </c>
       <c r="D2" t="n">
-        <v>9.519025740377073</v>
+        <v>14.47390640371073</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42954783057037</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="C3" t="n">
-        <v>15.79632056133118</v>
+        <v>54.01575868765951</v>
       </c>
       <c r="D3" t="n">
-        <v>5.360342465187586</v>
+        <v>8.8799079849124</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.63749841742144</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>45.69544689416779</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39918236158493</v>
+        <v>11.67606890525911</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1486605988858</v>
+        <v>59.93715371366346</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57637439548058</v>
+        <v>0.778404593683941</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.060909415392308</v>
+        <v>2.635992585902686</v>
       </c>
       <c r="C2" t="n">
-        <v>7.099999397112932</v>
+        <v>11.73286681345363</v>
       </c>
       <c r="D2" t="n">
-        <v>8.745408549430588</v>
+        <v>19.59568417676634</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.31021657900877</v>
+        <v>13.66101930459437</v>
       </c>
       <c r="C3" t="n">
-        <v>20.95049600862693</v>
+        <v>64.97697180557515</v>
       </c>
       <c r="D3" t="n">
-        <v>12.06077054667207</v>
+        <v>19.38460842035327</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.97816487079509</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C4" t="n">
-        <v>25.00216878405352</v>
+        <v>86.90136153681492</v>
       </c>
       <c r="D4" t="n">
-        <v>17.88057093744716</v>
+        <v>18.86330038939822</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.18020927588745</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4439804237546</v>
+        <v>13.61974463626379</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16115394305197</v>
+        <v>73.70685332566283</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25136429973781</v>
+        <v>1.602322898383975</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.767366851822511</v>
+        <v>1.389173001509237</v>
       </c>
       <c r="C2" t="n">
-        <v>5.203262832508095</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="D2" t="n">
-        <v>10.98084807200057</v>
+        <v>20.74236549532661</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.61041039233004</v>
+        <v>11.08884031946772</v>
       </c>
       <c r="C3" t="n">
-        <v>25.00020528864503</v>
+        <v>53.10764206123121</v>
       </c>
       <c r="D3" t="n">
-        <v>16.25774198232718</v>
+        <v>30.56180603320321</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.62151271671301</v>
+        <v>19.98641976305657</v>
       </c>
       <c r="C4" t="n">
-        <v>41.17253522070273</v>
+        <v>132.3366452893573</v>
       </c>
       <c r="D4" t="n">
-        <v>19.92260616228052</v>
+        <v>24.15982925380975</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.44427404613408</v>
+        <v>9.817477042468106</v>
       </c>
       <c r="C5" t="n">
-        <v>28.56885819358219</v>
+        <v>95.20498361933444</v>
       </c>
       <c r="D5" t="n">
-        <v>28.8879261974624</v>
+        <v>26.94897448157495</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.08056973167303</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.60177995163684</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7409577619093</v>
+        <v>14.81349712837038</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1198423476467</v>
+        <v>87.23503864484778</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02228732857279</v>
+        <v>2.46891618806173</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.358378969779091</v>
+        <v>2.971750300755095</v>
       </c>
       <c r="C2" t="n">
-        <v>9.535715451349269</v>
+        <v>9.221556185990289</v>
       </c>
       <c r="D2" t="n">
-        <v>14.97361598517235</v>
+        <v>21.94696992843745</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81381209355838</v>
+        <v>7.618362184955249</v>
       </c>
       <c r="C3" t="n">
-        <v>22.18258937745668</v>
+        <v>34.47897937314798</v>
       </c>
       <c r="D3" t="n">
-        <v>20.98485717827557</v>
+        <v>39.52516257297659</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.41654843070368</v>
+        <v>20.90533561423158</v>
       </c>
       <c r="C4" t="n">
-        <v>53.34817024877168</v>
+        <v>132.6684760133927</v>
       </c>
       <c r="D4" t="n">
-        <v>23.18986252201391</v>
+        <v>33.5021404074224</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.08489763311751</v>
+        <v>19.8067599331794</v>
       </c>
       <c r="C5" t="n">
-        <v>54.68334712654735</v>
+        <v>175.7819264453914</v>
       </c>
       <c r="D5" t="n">
-        <v>29.72241174607219</v>
+        <v>29.23153789394879</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.04782790006761</v>
+        <v>8.93586760405447</v>
       </c>
       <c r="C6" t="n">
-        <v>29.54471541160352</v>
+        <v>83.07941772418209</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>40.84561323518855</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07230560068284</v>
+        <v>16.02771628622962</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9002793949309</v>
+        <v>100.3841177927013</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884687847879175</v>
+        <v>3.374256060258867</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.935466693426968</v>
+        <v>2.438661297349077</v>
       </c>
       <c r="C2" t="n">
-        <v>8.448920742748049</v>
+        <v>9.044841599225864</v>
       </c>
       <c r="D2" t="n">
-        <v>15.93965572615121</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.20865459711484</v>
+        <v>8.811185645615124</v>
       </c>
       <c r="C3" t="n">
-        <v>29.03027961457818</v>
+        <v>35.06802799569606</v>
       </c>
       <c r="D3" t="n">
-        <v>26.05558407071035</v>
+        <v>46.91281404743384</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.55096575072749</v>
+        <v>17.58702837387736</v>
       </c>
       <c r="C4" t="n">
-        <v>45.74158903626739</v>
+        <v>108.4193077184965</v>
       </c>
       <c r="D4" t="n">
-        <v>24.38955821660351</v>
+        <v>44.43979158043612</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.50718801466389</v>
+        <v>25.35363446217388</v>
       </c>
       <c r="C5" t="n">
-        <v>58.48761948050374</v>
+        <v>208.5232123820226</v>
       </c>
       <c r="D5" t="n">
-        <v>25.54998400302325</v>
+        <v>34.06664533736433</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.26166897314417</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>40.13090090649688</v>
+        <v>178.7576037369635</v>
       </c>
       <c r="D6" t="n">
-        <v>29.98748362621883</v>
+        <v>35.09944392223197</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>20.78065365579224</v>
+        <v>66.53402366451058</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.71718421238145</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.13308538608361</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065595775749789</v>
+        <v>17.25486242715114</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23996039765427</v>
+        <v>113.01934889784</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299196831812342</v>
+        <v>4.313715606787786</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.531567476354029</v>
+        <v>2.072469403665017</v>
       </c>
       <c r="C2" t="n">
-        <v>10.16599747747572</v>
+        <v>15.71581724958294</v>
       </c>
       <c r="D2" t="n">
-        <v>19.02921575141593</v>
+        <v>34.04897387868787</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.48831382410494</v>
+        <v>8.403760348352696</v>
       </c>
       <c r="C3" t="n">
-        <v>31.66136346195963</v>
+        <v>34.87167845484671</v>
       </c>
       <c r="D3" t="n">
-        <v>33.53650157707104</v>
+        <v>55.92034923389832</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>17.08928228782423</v>
       </c>
       <c r="C4" t="n">
-        <v>63.06060028688537</v>
+        <v>98.20913159432968</v>
       </c>
       <c r="D4" t="n">
-        <v>32.80019079888594</v>
+        <v>54.56062866351648</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.99301425954582</v>
+        <v>25.69724615866027</v>
       </c>
       <c r="C5" t="n">
-        <v>74.24467013366505</v>
+        <v>204.1544350981243</v>
       </c>
       <c r="D5" t="n">
-        <v>29.05973204570559</v>
+        <v>40.91433557448583</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.73339089726815</v>
+        <v>24.2717484920939</v>
       </c>
       <c r="C6" t="n">
-        <v>72.29197394991814</v>
+        <v>244.2872995000296</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.01346673041897</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>43.23813239043802</v>
+        <v>150.4950508271063</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>24.28352946454485</v>
+        <v>51.98844967838984</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.292259561152473</v>
+        <v>17.60713549030647</v>
       </c>
       <c r="C21" t="n">
-        <v>76.56872539210097</v>
+        <v>125.0106619811759</v>
       </c>
       <c r="D21" t="n">
-        <v>6.380727116008414</v>
+        <v>5.282140647091939</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.895975801078843</v>
+        <v>2.000801821255</v>
       </c>
       <c r="C2" t="n">
-        <v>11.90074567087984</v>
+        <v>10.43499634843935</v>
       </c>
       <c r="D2" t="n">
-        <v>24.33556209286994</v>
+        <v>27.39566968700725</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.06616231127881</v>
+        <v>11.03975293425538</v>
       </c>
       <c r="C3" t="n">
-        <v>36.55537576762998</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="D3" t="n">
-        <v>40.97814917526187</v>
+        <v>59.14048170382786</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.21983903695583</v>
+        <v>12.34155039008665</v>
       </c>
       <c r="C4" t="n">
-        <v>72.8368439257751</v>
+        <v>157.530254875739</v>
       </c>
       <c r="D4" t="n">
-        <v>41.92553570986004</v>
+        <v>50.62971085571225</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.10439371848221</v>
+        <v>13.67083678163684</v>
       </c>
       <c r="C5" t="n">
-        <v>98.86199381765383</v>
+        <v>145.9613399288945</v>
       </c>
       <c r="D5" t="n">
-        <v>34.70478134512475</v>
+        <v>33.64940256305943</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.27932473628739</v>
+        <v>8.412596077690921</v>
       </c>
       <c r="C6" t="n">
-        <v>98.01278205348032</v>
+        <v>99.09957676208155</v>
       </c>
       <c r="D6" t="n">
-        <v>34.01264921363075</v>
+        <v>25.1170332654504</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>76.77463396750906</v>
+        <v>36.53083207502382</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>26.64954143177966</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>42.89255719854314</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>12.63803819676919</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.505917542943735</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.31805174385296</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.505917542943735</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
